--- a/data/trans_orig/P1_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P1_R-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares unipersonales en 2007</t>
+          <t>Hogares unipersonales en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20732</t>
+          <t>21674</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>43098</t>
+          <t>43909</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>24266</t>
+          <t>23345</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>46717</t>
+          <t>45582</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>50567</t>
+          <t>49449</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>80204</t>
+          <t>81333</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>15,24%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>229912</t>
+          <t>229101</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>252278</t>
+          <t>251336</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>83,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>214121</t>
+          <t>215256</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>236572</t>
+          <t>237493</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>82,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>91,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>453644</t>
+          <t>452515</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>483281</t>
+          <t>484399</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>84,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,74%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24674</t>
+          <t>25553</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>49416</t>
+          <t>51618</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33942</t>
+          <t>34362</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>61418</t>
+          <t>60908</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>65111</t>
+          <t>66330</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>102814</t>
+          <t>102334</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,26%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>443659</t>
+          <t>441457</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>468401</t>
+          <t>467522</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>89,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>442531</t>
+          <t>443041</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>470007</t>
+          <t>469587</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>894210</t>
+          <t>894690</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>931913</t>
+          <t>930694</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>89,74%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,35%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14408</t>
+          <t>13791</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>33333</t>
+          <t>34647</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19626</t>
+          <t>20106</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>40808</t>
+          <t>42916</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>38916</t>
+          <t>37651</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>67674</t>
+          <t>66196</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,12%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>285513</t>
+          <t>284199</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>304438</t>
+          <t>305055</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>89,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>294604</t>
+          <t>292496</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>315786</t>
+          <t>315306</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>87,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>586584</t>
+          <t>588062</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>615342</t>
+          <t>616607</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>89,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,25%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13160</t>
+          <t>12089</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>31212</t>
+          <t>30327</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25851</t>
+          <t>26162</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>48420</t>
+          <t>49002</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>43183</t>
+          <t>43662</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>71188</t>
+          <t>73017</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>10,0%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>327459</t>
+          <t>328344</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>345511</t>
+          <t>346582</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>323036</t>
+          <t>322454</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>345605</t>
+          <t>345294</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,96%</t>
+          <t>86,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>658939</t>
+          <t>657110</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>686944</t>
+          <t>686465</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,02%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11996</t>
+          <t>11616</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28850</t>
+          <t>27998</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3572</t>
+          <t>3861</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14960</t>
+          <t>15342</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>18918</t>
+          <t>18287</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>37717</t>
+          <t>39607</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,64%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>174458</t>
+          <t>175310</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>191312</t>
+          <t>191692</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,81%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>192708</t>
+          <t>192326</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>204096</t>
+          <t>203807</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>373259</t>
+          <t>371369</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>392058</t>
+          <t>392689</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>90,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,55%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14869</t>
+          <t>14116</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>33507</t>
+          <t>31400</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>22067</t>
+          <t>21058</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>43808</t>
+          <t>43240</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>41406</t>
+          <t>40714</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>69434</t>
+          <t>67201</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,24%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>237304</t>
+          <t>239411</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>255942</t>
+          <t>256695</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>88,41%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>234336</t>
+          <t>234904</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>256077</t>
+          <t>257086</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>84,25%</t>
+          <t>84,45%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>479521</t>
+          <t>481754</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>507549</t>
+          <t>508241</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,35%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,58%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>31838</t>
+          <t>31375</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>61090</t>
+          <t>58485</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>40898</t>
+          <t>40504</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>67713</t>
+          <t>68291</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>78867</t>
+          <t>79416</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>117994</t>
+          <t>120207</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,59%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>553937</t>
+          <t>556542</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>583189</t>
+          <t>583652</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>570506</t>
+          <t>569928</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>597321</t>
+          <t>597715</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>89,3%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1135252</t>
+          <t>1133039</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1174379</t>
+          <t>1173830</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>90,41%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,66%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>33838</t>
+          <t>33441</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>59503</t>
+          <t>58920</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>44863</t>
+          <t>43838</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>73802</t>
+          <t>72832</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>84733</t>
+          <t>83349</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>123937</t>
+          <t>126284</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,27%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>684292</t>
+          <t>684875</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>709957</t>
+          <t>710354</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>709709</t>
+          <t>710679</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>738648</t>
+          <t>739673</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>90,7%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1403369</t>
+          <t>1401022</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1442573</t>
+          <t>1443957</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,54%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>209536</t>
+          <t>208080</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>267820</t>
+          <t>268121</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>263461</t>
+          <t>264324</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>331569</t>
+          <t>329422</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>489298</t>
+          <t>494099</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>577801</t>
+          <t>579992</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,71%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3008723</t>
+          <t>3008422</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3067007</t>
+          <t>3068463</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3047628</t>
+          <t>3049775</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3115736</t>
+          <t>3114873</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6077940</t>
+          <t>6075749</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6166443</t>
+          <t>6161642</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,58%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares unipersonales en 2012</t>
+          <t>Hogares unipersonales en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15105</t>
+          <t>15760</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33068</t>
+          <t>34833</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17343</t>
+          <t>17485</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38751</t>
+          <t>37678</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>35363</t>
+          <t>36928</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>63263</t>
+          <t>63998</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>11,0%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>261670</t>
+          <t>259905</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>279633</t>
+          <t>278978</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>88,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>248494</t>
+          <t>249567</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>269902</t>
+          <t>269760</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>86,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>518720</t>
+          <t>517985</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>546620</t>
+          <t>545055</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>89,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>93,65%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16088</t>
+          <t>16949</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>41783</t>
+          <t>40874</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>27348</t>
+          <t>26534</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>50095</t>
+          <t>50222</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>49280</t>
+          <t>47348</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>83975</t>
+          <t>80440</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>7,82%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>463744</t>
+          <t>464653</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>489439</t>
+          <t>488578</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>473670</t>
+          <t>473543</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>496417</t>
+          <t>497231</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>90,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>945317</t>
+          <t>948852</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>980012</t>
+          <t>981944</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,4%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16146</t>
+          <t>16825</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35469</t>
+          <t>36693</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>35444</t>
+          <t>34755</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>61188</t>
+          <t>60691</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>55614</t>
+          <t>56712</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>89279</t>
+          <t>90240</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,57%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>288577</t>
+          <t>287353</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>307900</t>
+          <t>307221</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>88,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>279832</t>
+          <t>280329</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>305576</t>
+          <t>306265</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,06%</t>
+          <t>82,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>89,81%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>575787</t>
+          <t>574826</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>609452</t>
+          <t>608354</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,58%</t>
+          <t>86,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,47%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24934</t>
+          <t>25440</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>48223</t>
+          <t>49842</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24598</t>
+          <t>24256</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>48393</t>
+          <t>46455</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>56206</t>
+          <t>55213</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>89002</t>
+          <t>88101</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,55%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>325759</t>
+          <t>324140</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>349048</t>
+          <t>348542</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,11%</t>
+          <t>86,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>340558</t>
+          <t>342496</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>364353</t>
+          <t>364695</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>673931</t>
+          <t>674832</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>706727</t>
+          <t>707720</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>88,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>92,76%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>5235</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17622</t>
+          <t>17950</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8478</t>
+          <t>8847</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23557</t>
+          <t>24610</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16769</t>
+          <t>17099</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>37464</t>
+          <t>37109</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,59%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>194996</t>
+          <t>194668</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>207435</t>
+          <t>207383</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>196034</t>
+          <t>194981</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>211113</t>
+          <t>210744</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>88,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>394745</t>
+          <t>395100</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>415440</t>
+          <t>415110</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,04%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13312</t>
+          <t>13411</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>30764</t>
+          <t>31458</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>26176</t>
+          <t>26218</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>49791</t>
+          <t>49327</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>43922</t>
+          <t>44375</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>75725</t>
+          <t>73362</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,24%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>243217</t>
+          <t>242523</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>260669</t>
+          <t>260570</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>88,52%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>230240</t>
+          <t>230704</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>253855</t>
+          <t>253813</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>82,22%</t>
+          <t>82,39%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>478287</t>
+          <t>480650</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>510090</t>
+          <t>509637</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,33%</t>
+          <t>86,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>91,99%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>48284</t>
+          <t>47860</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>79290</t>
+          <t>79143</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>59337</t>
+          <t>62283</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>97086</t>
+          <t>96687</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>117185</t>
+          <t>116600</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>164364</t>
+          <t>163689</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,07%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>583498</t>
+          <t>583645</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>614504</t>
+          <t>614928</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>596767</t>
+          <t>597166</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>634516</t>
+          <t>631570</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>86,07%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1192277</t>
+          <t>1192952</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1239456</t>
+          <t>1240041</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,41%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>66368</t>
+          <t>64376</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>102278</t>
+          <t>101878</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>64696</t>
+          <t>64214</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>100917</t>
+          <t>99057</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>136974</t>
+          <t>139431</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>183846</t>
+          <t>187365</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,69%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>676820</t>
+          <t>677220</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>712730</t>
+          <t>714722</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>86,92%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>722936</t>
+          <t>724796</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>759157</t>
+          <t>759639</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>87,98%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1419105</t>
+          <t>1415586</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1465977</t>
+          <t>1463520</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,31%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,3%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>252379</t>
+          <t>252517</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>322286</t>
+          <t>323157</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>316856</t>
+          <t>319615</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>391205</t>
+          <t>393320</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>591395</t>
+          <t>592116</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>689537</t>
+          <t>694341</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,94%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3104493</t>
+          <t>3103622</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3174400</t>
+          <t>3174262</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3167104</t>
+          <t>3164989</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3241453</t>
+          <t>3238694</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>88,95%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6295551</t>
+          <t>6290747</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6393693</t>
+          <t>6392972</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>90,06%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,52%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares unipersonales en 2016</t>
+          <t>Hogares unipersonales en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24126</t>
+          <t>24099</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>46181</t>
+          <t>48080</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25123</t>
+          <t>25066</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>47941</t>
+          <t>49561</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>54462</t>
+          <t>54307</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>87714</t>
+          <t>89048</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>15,29%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>247580</t>
+          <t>245681</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>269635</t>
+          <t>269662</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,28%</t>
+          <t>83,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>240762</t>
+          <t>239142</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>263580</t>
+          <t>263637</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,39%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>494750</t>
+          <t>493416</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>528002</t>
+          <t>528157</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,94%</t>
+          <t>84,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,68%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>29703</t>
+          <t>29589</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>55508</t>
+          <t>53238</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26998</t>
+          <t>28149</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>53456</t>
+          <t>55412</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>62574</t>
+          <t>63040</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>98718</t>
+          <t>99387</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,69%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>447067</t>
+          <t>449337</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>472872</t>
+          <t>472986</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>469628</t>
+          <t>467672</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>496086</t>
+          <t>494935</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>926941</t>
+          <t>926272</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>963085</t>
+          <t>962619</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>93,85%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21364</t>
+          <t>20198</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>41008</t>
+          <t>41110</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>34092</t>
+          <t>35097</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>60724</t>
+          <t>61301</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>62022</t>
+          <t>60969</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>94920</t>
+          <t>93180</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,23%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>277557</t>
+          <t>277455</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>297201</t>
+          <t>298367</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>87,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>275585</t>
+          <t>275008</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>302217</t>
+          <t>301212</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,94%</t>
+          <t>81,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>559954</t>
+          <t>561694</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>592852</t>
+          <t>593905</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>85,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,69%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31117</t>
+          <t>30824</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>56237</t>
+          <t>54063</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38805</t>
+          <t>38002</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>68483</t>
+          <t>67199</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>75892</t>
+          <t>76077</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>113928</t>
+          <t>113907</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,04%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>313727</t>
+          <t>315901</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>338847</t>
+          <t>339140</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>85,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>318800</t>
+          <t>320084</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>348478</t>
+          <t>349281</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,32%</t>
+          <t>82,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>643319</t>
+          <t>643340</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>681355</t>
+          <t>681170</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>84,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>89,95%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>21445</t>
+          <t>21584</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>42283</t>
+          <t>42294</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,7 +8766,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11848</t>
+          <t>11659</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30021</t>
+          <t>30246</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>37427</t>
+          <t>36714</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>65110</t>
+          <t>63157</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>14,69%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>168938</t>
+          <t>168927</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>189776</t>
+          <t>189637</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8884,7 +8884,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>89,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>188566</t>
+          <t>188341</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>206739</t>
+          <t>206928</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>86,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>364698</t>
+          <t>366651</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>392381</t>
+          <t>393094</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,85%</t>
+          <t>85,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>91,46%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>19867</t>
+          <t>20874</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>40972</t>
+          <t>42604</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>25600</t>
+          <t>25537</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>48936</t>
+          <t>48729</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>51692</t>
+          <t>50756</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>82027</t>
+          <t>82148</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,32%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>222151</t>
+          <t>220519</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>243256</t>
+          <t>242249</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>84,43%</t>
+          <t>83,81%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>224179</t>
+          <t>224386</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>247515</t>
+          <t>247578</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>82,08%</t>
+          <t>82,16%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,63%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>454211</t>
+          <t>454090</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>484546</t>
+          <t>485482</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,7%</t>
+          <t>84,68%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,53%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>102158</t>
+          <t>102164</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>143907</t>
+          <t>145156</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9457,7 +9457,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>118395</t>
+          <t>117806</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>164500</t>
+          <t>162285</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,42 +9487,42 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
+          <t>17,04%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>23,48%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>260005</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>230907</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>292038</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>19,29%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
           <t>17,13%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>23,8%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>260005</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>229071</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>292078</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>19,29%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>17,0%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>512651</t>
+          <t>511402</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>554400</t>
+          <t>554394</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,7 +9565,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>78,08%</t>
+          <t>77,89%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>526794</t>
+          <t>529009</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>572899</t>
+          <t>573488</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,47 +9600,47 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>76,2%</t>
+          <t>76,52%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
+          <t>82,96%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>995</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>1087847</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>1055814</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>1116945</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>80,71%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>78,33%</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
           <t>82,87%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>995</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>1087847</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>1055774</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>1118781</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>80,71%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>78,33%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>83,0%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>79341</t>
+          <t>79176</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>117198</t>
+          <t>116413</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>82309</t>
+          <t>81820</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>122523</t>
+          <t>120704</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>173154</t>
+          <t>171705</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>227413</t>
+          <t>226398</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,11%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>661385</t>
+          <t>662170</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>699242</t>
+          <t>699407</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>85,05%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>703644</t>
+          <t>705463</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>743858</t>
+          <t>744347</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>85,17%</t>
+          <t>85,39%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1377337</t>
+          <t>1378352</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1431596</t>
+          <t>1433045</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>89,3%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>391908</t>
+          <t>385915</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>467061</t>
+          <t>462648</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>422524</t>
+          <t>426087</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>510518</t>
+          <t>512579</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>834114</t>
+          <t>834380</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>953145</t>
+          <t>950192</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10213,7 +10213,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,69%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2927289</t>
+          <t>2931702</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3002442</t>
+          <t>3008435</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>86,24%</t>
+          <t>86,37%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>88,63%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3034024</t>
+          <t>3031963</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3122018</t>
+          <t>3118455</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>85,54%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>87,98%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5985747</t>
+          <t>5988700</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6104778</t>
+          <t>6104512</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,7 +10321,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>86,26%</t>
+          <t>86,31%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares unipersonales en 2023</t>
+          <t>Hogares unipersonales en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>41050</t>
+          <t>41023</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>73724</t>
+          <t>73496</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>36410</t>
+          <t>36199</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>53344</t>
+          <t>53529</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>83159</t>
+          <t>81649</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>123385</t>
+          <t>118150</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>19,66%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>237719</t>
+          <t>237947</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>270393</t>
+          <t>270420</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,33%</t>
+          <t>76,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,82%</t>
+          <t>86,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>236291</t>
+          <t>236106</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>253225</t>
+          <t>253436</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,58%</t>
+          <t>81,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>87,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>477692</t>
+          <t>482927</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>517918</t>
+          <t>519428</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,47%</t>
+          <t>80,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>86,42%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>61296</t>
+          <t>61682</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>101063</t>
+          <t>101745</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>73609</t>
+          <t>72913</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>102427</t>
+          <t>103255</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>142813</t>
+          <t>143882</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>192039</t>
+          <t>193823</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,76%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>417327</t>
+          <t>416645</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>457094</t>
+          <t>456708</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>80,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,18%</t>
+          <t>88,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>412542</t>
+          <t>411714</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>441360</t>
+          <t>442056</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,11%</t>
+          <t>79,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,71%</t>
+          <t>85,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>841320</t>
+          <t>839536</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>890546</t>
+          <t>889477</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,42%</t>
+          <t>81,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>86,08%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>47500</t>
+          <t>47955</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>74383</t>
+          <t>73736</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>63965</t>
+          <t>63134</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>88004</t>
+          <t>87360</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>116154</t>
+          <t>117871</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>152551</t>
+          <t>153029</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>23,01%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>241667</t>
+          <t>242314</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>268550</t>
+          <t>268095</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,46%</t>
+          <t>76,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,97%</t>
+          <t>84,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>261124</t>
+          <t>261768</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>285163</t>
+          <t>285994</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,79%</t>
+          <t>74,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>81,92%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>512627</t>
+          <t>512149</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>549024</t>
+          <t>547307</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,07%</t>
+          <t>76,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>82,54%</t>
+          <t>82,28%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>52259</t>
+          <t>52674</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>88222</t>
+          <t>86615</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>50402</t>
+          <t>47671</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>106176</t>
+          <t>105493</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>107118</t>
+          <t>106087</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>179685</t>
+          <t>178899</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,69%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>224335</t>
+          <t>225942</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>260298</t>
+          <t>259883</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,77%</t>
+          <t>72,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,28%</t>
+          <t>83,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>369542</t>
+          <t>370225</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>425316</t>
+          <t>428047</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,68%</t>
+          <t>77,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,41%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>608589</t>
+          <t>609375</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>681156</t>
+          <t>682187</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,21%</t>
+          <t>77,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,41%</t>
+          <t>86,54%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>35611</t>
+          <t>34892</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>54912</t>
+          <t>54133</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>22626</t>
+          <t>23169</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>53998</t>
+          <t>55331</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>57948</t>
+          <t>54335</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>101411</t>
+          <t>100247</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>22,91%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>123830</t>
+          <t>124609</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>143131</t>
+          <t>143850</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>69,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>80,08%</t>
+          <t>80,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>204781</t>
+          <t>203448</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>236153</t>
+          <t>235610</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>79,13%</t>
+          <t>78,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>91,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>336110</t>
+          <t>337274</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>379573</t>
+          <t>383186</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>76,82%</t>
+          <t>77,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>87,58%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>60387</t>
+          <t>60067</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>86353</t>
+          <t>86218</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>45035</t>
+          <t>44339</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>62964</t>
+          <t>63406</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>111182</t>
+          <t>110087</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>141345</t>
+          <t>142269</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>27,01%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>183283</t>
+          <t>183418</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>209249</t>
+          <t>209569</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>67,97%</t>
+          <t>68,02%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>77,6%</t>
+          <t>77,72%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>194092</t>
+          <t>193650</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>212021</t>
+          <t>212717</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>75,51%</t>
+          <t>75,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>82,48%</t>
+          <t>82,75%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>385347</t>
+          <t>384423</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>415510</t>
+          <t>416605</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>72,99%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>78,89%</t>
+          <t>79,1%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>90892</t>
+          <t>90810</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>131548</t>
+          <t>129231</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>45964</t>
+          <t>42336</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>121158</t>
+          <t>120909</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>122515</t>
+          <t>125588</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>235075</t>
+          <t>240460</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>16,32%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>492731</t>
+          <t>495048</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>533387</t>
+          <t>533469</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>78,93%</t>
+          <t>79,3%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>728107</t>
+          <t>728356</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>803301</t>
+          <t>806929</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>85,73%</t>
+          <t>85,76%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1238469</t>
+          <t>1233084</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1351029</t>
+          <t>1347956</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>84,05%</t>
+          <t>83,68%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>91,48%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>36452</t>
+          <t>39422</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>130215</t>
+          <t>132333</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>115072</t>
+          <t>115610</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>150375</t>
+          <t>151426</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>140912</t>
+          <t>139440</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>274039</t>
+          <t>272983</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,58%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>798505</t>
+          <t>796387</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>892268</t>
+          <t>889298</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>85,98%</t>
+          <t>85,75%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>567356</t>
+          <t>566305</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>602659</t>
+          <t>602121</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>79,05%</t>
+          <t>78,9%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>83,97%</t>
+          <t>83,89%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1372413</t>
+          <t>1373469</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1505540</t>
+          <t>1507012</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>83,36%</t>
+          <t>83,42%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,53%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>446849</t>
+          <t>465285</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>643924</t>
+          <t>645945</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>488579</t>
+          <t>493102</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>659073</t>
+          <t>660438</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1025000</t>
+          <t>1029354</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1279680</t>
+          <t>1279637</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,7 +13531,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2815893</t>
+          <t>2813872</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3012968</t>
+          <t>2994532</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>81,39%</t>
+          <t>81,33%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>87,08%</t>
+          <t>86,55%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3053207</t>
+          <t>3051842</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3223701</t>
+          <t>3219178</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>82,25%</t>
+          <t>82,21%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>86,84%</t>
+          <t>86,72%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5892417</t>
+          <t>5892460</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6147097</t>
+          <t>6142743</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13649,7 +13649,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>85,71%</t>
+          <t>85,65%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P1_R-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21674</t>
+          <t>21043</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>43909</t>
+          <t>43122</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23345</t>
+          <t>23233</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>45582</t>
+          <t>45989</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>49449</t>
+          <t>48997</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>81333</t>
+          <t>79874</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>14,96%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>229101</t>
+          <t>229888</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>251336</t>
+          <t>251967</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,92%</t>
+          <t>84,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>215256</t>
+          <t>214849</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>237493</t>
+          <t>237605</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,52%</t>
+          <t>82,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>452515</t>
+          <t>453974</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>484399</t>
+          <t>484851</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>85,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>90,82%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25553</t>
+          <t>24303</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>51618</t>
+          <t>50254</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>34362</t>
+          <t>35338</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>60908</t>
+          <t>60047</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>66330</t>
+          <t>64622</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>102334</t>
+          <t>100486</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,08%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>441457</t>
+          <t>442821</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>467522</t>
+          <t>468772</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>89,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>443041</t>
+          <t>443902</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>469587</t>
+          <t>468611</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>88,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>894690</t>
+          <t>896538</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>930694</t>
+          <t>932402</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,74%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,52%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13791</t>
+          <t>13424</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34647</t>
+          <t>32772</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20106</t>
+          <t>20064</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>42916</t>
+          <t>40501</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>37651</t>
+          <t>39686</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>66196</t>
+          <t>66922</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,23%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>284199</t>
+          <t>286074</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>305055</t>
+          <t>305422</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>292496</t>
+          <t>294911</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>315306</t>
+          <t>315348</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>87,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>588062</t>
+          <t>587336</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>616607</t>
+          <t>614572</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>93,93%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12089</t>
+          <t>12581</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30327</t>
+          <t>31795</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26162</t>
+          <t>26072</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>49002</t>
+          <t>49619</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>43662</t>
+          <t>43459</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>73017</t>
+          <t>72834</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,98%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>328344</t>
+          <t>326876</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>346582</t>
+          <t>346090</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>322454</t>
+          <t>321837</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>345294</t>
+          <t>345384</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,81%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>657110</t>
+          <t>657293</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>686465</t>
+          <t>686668</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>94,05%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11616</t>
+          <t>11862</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27998</t>
+          <t>28945</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3861</t>
+          <t>3889</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15342</t>
+          <t>14294</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>18287</t>
+          <t>19116</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>39607</t>
+          <t>38958</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,48%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>175310</t>
+          <t>174363</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>191692</t>
+          <t>191446</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,23%</t>
+          <t>85,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>192326</t>
+          <t>193374</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>203807</t>
+          <t>203779</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>371369</t>
+          <t>372018</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>392689</t>
+          <t>391860</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,35%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14116</t>
+          <t>14724</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>31400</t>
+          <t>32470</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>21058</t>
+          <t>21872</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>43240</t>
+          <t>43172</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>40714</t>
+          <t>40042</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>67201</t>
+          <t>68718</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,52%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>239411</t>
+          <t>238341</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>256695</t>
+          <t>256087</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>88,01%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>234904</t>
+          <t>234972</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>257086</t>
+          <t>256272</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>84,48%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>481754</t>
+          <t>480237</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>508241</t>
+          <t>508913</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>87,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,71%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>31375</t>
+          <t>31634</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>58485</t>
+          <t>58619</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>40504</t>
+          <t>40107</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>68291</t>
+          <t>68591</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>79416</t>
+          <t>78541</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>120207</t>
+          <t>118203</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,43%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>556542</t>
+          <t>556408</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>583652</t>
+          <t>583393</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>569928</t>
+          <t>569628</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>597715</t>
+          <t>598112</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1133039</t>
+          <t>1135043</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1173830</t>
+          <t>1174705</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,73%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>33441</t>
+          <t>33077</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>58920</t>
+          <t>59605</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>43838</t>
+          <t>45824</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>72832</t>
+          <t>76592</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>83349</t>
+          <t>84290</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>126284</t>
+          <t>123566</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,09%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>684875</t>
+          <t>684190</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>710354</t>
+          <t>710718</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>710679</t>
+          <t>706919</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>739673</t>
+          <t>737687</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>90,22%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1401022</t>
+          <t>1403740</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1443957</t>
+          <t>1443016</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,48%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>208080</t>
+          <t>209412</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>268121</t>
+          <t>271884</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>264324</t>
+          <t>261588</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>329422</t>
+          <t>329584</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,7 +3527,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>494099</t>
+          <t>489979</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>579992</t>
+          <t>582606</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,75%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3008422</t>
+          <t>3004659</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3068463</t>
+          <t>3067131</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3049775</t>
+          <t>3049613</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3114873</t>
+          <t>3117609</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3645,7 +3645,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6075749</t>
+          <t>6073135</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6161642</t>
+          <t>6165762</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,64%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15760</t>
+          <t>16356</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34833</t>
+          <t>33524</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17485</t>
+          <t>16613</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37678</t>
+          <t>37642</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>36928</t>
+          <t>36335</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>63998</t>
+          <t>65054</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,18%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>259905</t>
+          <t>261214</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>278978</t>
+          <t>278382</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,18%</t>
+          <t>88,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>249567</t>
+          <t>249603</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>269760</t>
+          <t>270632</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,88%</t>
+          <t>86,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>517985</t>
+          <t>516929</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>545055</t>
+          <t>545648</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,0%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,76%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16949</t>
+          <t>16752</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>40874</t>
+          <t>41182</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26534</t>
+          <t>27302</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>50222</t>
+          <t>51438</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>47348</t>
+          <t>48930</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>80440</t>
+          <t>81088</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,88%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>464653</t>
+          <t>464345</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>488578</t>
+          <t>488775</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>473543</t>
+          <t>472327</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>497231</t>
+          <t>496463</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>948852</t>
+          <t>948204</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>981944</t>
+          <t>980362</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,25%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16825</t>
+          <t>16015</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>36693</t>
+          <t>36133</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>34755</t>
+          <t>34466</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>60691</t>
+          <t>60568</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>56712</t>
+          <t>56943</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>90240</t>
+          <t>90056</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,54%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>287353</t>
+          <t>287913</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>307221</t>
+          <t>308031</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>280329</t>
+          <t>280452</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>306265</t>
+          <t>306554</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,2%</t>
+          <t>82,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>574826</t>
+          <t>575010</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>608354</t>
+          <t>608123</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,44%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>25440</t>
+          <t>25840</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>49842</t>
+          <t>50088</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24256</t>
+          <t>23747</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>46455</t>
+          <t>46359</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>55213</t>
+          <t>55144</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>88101</t>
+          <t>88526</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,6%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>324140</t>
+          <t>323894</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>348542</t>
+          <t>348142</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,67%</t>
+          <t>86,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>342496</t>
+          <t>342592</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>364695</t>
+          <t>365204</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>88,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>674832</t>
+          <t>674407</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>707720</t>
+          <t>707789</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>88,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,77%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5235</t>
+          <t>5207</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17950</t>
+          <t>17982</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8847</t>
+          <t>9725</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>24610</t>
+          <t>25113</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17099</t>
+          <t>17355</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>37109</t>
+          <t>37507</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,68%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>194668</t>
+          <t>194636</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>207383</t>
+          <t>207411</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>194981</t>
+          <t>194478</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>210744</t>
+          <t>209866</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>88,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>395100</t>
+          <t>394702</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>415110</t>
+          <t>414854</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>95,98%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13411</t>
+          <t>13457</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>31458</t>
+          <t>32503</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>26218</t>
+          <t>27005</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>49327</t>
+          <t>49083</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>44375</t>
+          <t>42910</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>73362</t>
+          <t>73290</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,23%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>242523</t>
+          <t>241478</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>260570</t>
+          <t>260524</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>88,14%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>230704</t>
+          <t>230948</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>253813</t>
+          <t>253026</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>82,39%</t>
+          <t>82,47%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>90,36%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>480650</t>
+          <t>480722</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>509637</t>
+          <t>511102</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>86,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>92,25%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>47860</t>
+          <t>46522</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>79143</t>
+          <t>77621</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>62283</t>
+          <t>60969</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>96687</t>
+          <t>96904</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>116600</t>
+          <t>115398</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>163689</t>
+          <t>163985</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,09%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>583645</t>
+          <t>585167</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>614928</t>
+          <t>616266</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>88,29%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>597166</t>
+          <t>596949</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>631570</t>
+          <t>632884</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>86,07%</t>
+          <t>86,03%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>91,21%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1192952</t>
+          <t>1192656</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1240041</t>
+          <t>1241243</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,49%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>64376</t>
+          <t>64461</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>101878</t>
+          <t>100671</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>64214</t>
+          <t>63199</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>99057</t>
+          <t>98058</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>139431</t>
+          <t>139434</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>187365</t>
+          <t>190242</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6547,7 +6547,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,87%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>677220</t>
+          <t>678427</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>714722</t>
+          <t>714637</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>87,08%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>724796</t>
+          <t>725795</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>759639</t>
+          <t>760654</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>88,1%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1415586</t>
+          <t>1412709</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1463520</t>
+          <t>1463517</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,7 +6655,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>252517</t>
+          <t>255201</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>323157</t>
+          <t>322954</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>319615</t>
+          <t>318571</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>393320</t>
+          <t>393250</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,7 +6850,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>592116</t>
+          <t>595702</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>694341</t>
+          <t>691765</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,9%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3103622</t>
+          <t>3103825</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3174262</t>
+          <t>3171578</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3164989</t>
+          <t>3165059</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3238694</t>
+          <t>3239738</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6968,7 +6968,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>91,05%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6290747</t>
+          <t>6293323</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6392972</t>
+          <t>6389386</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,47%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24099</t>
+          <t>23773</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>48080</t>
+          <t>47209</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25066</t>
+          <t>24462</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>49561</t>
+          <t>49723</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>54307</t>
+          <t>54901</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>89048</t>
+          <t>87910</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,09%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>245681</t>
+          <t>246552</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>269662</t>
+          <t>269988</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>83,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>239142</t>
+          <t>238980</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>263637</t>
+          <t>264241</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,83%</t>
+          <t>82,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>493416</t>
+          <t>494554</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>528157</t>
+          <t>527563</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,57%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>29589</t>
+          <t>29818</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>53238</t>
+          <t>53911</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28149</t>
+          <t>28321</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>55412</t>
+          <t>53395</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>63040</t>
+          <t>63563</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>99387</t>
+          <t>99375</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,7 +7807,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>449337</t>
+          <t>448664</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>472986</t>
+          <t>472757</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,41%</t>
+          <t>89,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>467672</t>
+          <t>469689</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>494935</t>
+          <t>494763</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,41%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>926272</t>
+          <t>926284</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>962619</t>
+          <t>962096</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7925,7 +7925,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,8%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20198</t>
+          <t>21317</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>41110</t>
+          <t>41517</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>35097</t>
+          <t>34648</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>61301</t>
+          <t>59914</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>60969</t>
+          <t>60266</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>93180</t>
+          <t>94179</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,38%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>277455</t>
+          <t>277048</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>298367</t>
+          <t>297248</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,1%</t>
+          <t>86,97%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>275008</t>
+          <t>276395</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>301212</t>
+          <t>301661</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,77%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>89,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>561694</t>
+          <t>560695</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>593905</t>
+          <t>594608</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,77%</t>
+          <t>85,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,8%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30824</t>
+          <t>30444</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>54063</t>
+          <t>54358</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38002</t>
+          <t>38551</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>67199</t>
+          <t>67616</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>76077</t>
+          <t>75969</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>113907</t>
+          <t>114005</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,06%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>315901</t>
+          <t>315606</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>339140</t>
+          <t>339520</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>85,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>91,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>320084</t>
+          <t>319667</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>349281</t>
+          <t>348732</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,65%</t>
+          <t>82,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>90,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>643340</t>
+          <t>643242</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>681170</t>
+          <t>681278</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>84,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>89,97%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>21584</t>
+          <t>21628</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>42294</t>
+          <t>41797</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11659</t>
+          <t>12044</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30246</t>
+          <t>30997</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>36714</t>
+          <t>37919</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>63157</t>
+          <t>64810</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>15,08%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>168927</t>
+          <t>169424</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>189637</t>
+          <t>189593</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,98%</t>
+          <t>80,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>89,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>188341</t>
+          <t>187590</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>206928</t>
+          <t>206543</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>85,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>366651</t>
+          <t>364998</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>393094</t>
+          <t>391889</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,31%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>91,18%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>20874</t>
+          <t>19854</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>42604</t>
+          <t>41731</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>25537</t>
+          <t>26218</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>48729</t>
+          <t>49343</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>50756</t>
+          <t>51563</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>82148</t>
+          <t>81467</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,19%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>220519</t>
+          <t>221392</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>242249</t>
+          <t>243269</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>83,81%</t>
+          <t>84,14%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>224386</t>
+          <t>223772</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>247578</t>
+          <t>246897</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>82,16%</t>
+          <t>81,93%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>454090</t>
+          <t>454771</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>485482</t>
+          <t>484675</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,68%</t>
+          <t>84,81%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,38%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>102164</t>
+          <t>101336</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>145156</t>
+          <t>143505</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>117806</t>
+          <t>118177</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>162285</t>
+          <t>160912</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>230907</t>
+          <t>231478</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>292038</t>
+          <t>290222</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,53%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>511402</t>
+          <t>513053</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>554394</t>
+          <t>555222</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>78,14%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>84,57%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>529009</t>
+          <t>530382</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>573488</t>
+          <t>573117</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>76,52%</t>
+          <t>76,72%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>82,96%</t>
+          <t>82,9%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1055814</t>
+          <t>1057630</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1116945</t>
+          <t>1116374</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>78,33%</t>
+          <t>78,47%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>82,83%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>79176</t>
+          <t>79658</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>116413</t>
+          <t>117290</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>81820</t>
+          <t>83101</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>120704</t>
+          <t>122175</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>171705</t>
+          <t>172303</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>226398</t>
+          <t>226580</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,12%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>662170</t>
+          <t>661293</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>699407</t>
+          <t>698925</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>84,94%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>705463</t>
+          <t>703992</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>744347</t>
+          <t>743066</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>85,21%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1378352</t>
+          <t>1378170</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1433045</t>
+          <t>1432447</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>85,89%</t>
+          <t>85,88%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>89,26%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>385915</t>
+          <t>385870</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>462648</t>
+          <t>468053</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>426087</t>
+          <t>426715</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>512579</t>
+          <t>512088</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>834380</t>
+          <t>832352</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>950192</t>
+          <t>950207</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,7 +10208,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2931702</t>
+          <t>2926297</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3008435</t>
+          <t>3008480</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,7 +10251,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>86,21%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3031963</t>
+          <t>3032454</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3118455</t>
+          <t>3117827</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>85,54%</t>
+          <t>85,55%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5988700</t>
+          <t>5988685</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6104512</t>
+          <t>6106540</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>88,0%</t>
         </is>
       </c>
     </row>
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>54989</t>
+          <t>57835</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>41023</t>
+          <t>45272</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>73496</t>
+          <t>75117</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>43903</t>
+          <t>46800</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>36199</t>
+          <t>38502</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>53529</t>
+          <t>57669</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>98892</t>
+          <t>104635</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>81649</t>
+          <t>88967</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>118150</t>
+          <t>122299</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,26%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>256454</t>
+          <t>261010</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>237947</t>
+          <t>243728</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>270420</t>
+          <t>273573</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>81,86%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,4%</t>
+          <t>76,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,83%</t>
+          <t>85,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>245732</t>
+          <t>269261</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>236106</t>
+          <t>258392</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>253436</t>
+          <t>277559</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>84,84%</t>
+          <t>85,19%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,52%</t>
+          <t>81,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,5%</t>
+          <t>87,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>502185</t>
+          <t>530271</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>482927</t>
+          <t>512607</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>519428</t>
+          <t>545939</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>83,52%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,34%</t>
+          <t>80,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>85,99%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>79646</t>
+          <t>83945</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>61682</t>
+          <t>65109</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>101745</t>
+          <t>104906</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>86845</t>
+          <t>88673</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>72913</t>
+          <t>75158</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>103255</t>
+          <t>105965</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>166492</t>
+          <t>172618</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>143882</t>
+          <t>148240</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>193823</t>
+          <t>198060</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,39%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>438744</t>
+          <t>446702</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>416645</t>
+          <t>425741</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>456708</t>
+          <t>465538</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>84,64%</t>
+          <t>84,18%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,37%</t>
+          <t>80,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>87,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>428124</t>
+          <t>457821</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>411714</t>
+          <t>440529</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>442056</t>
+          <t>471336</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>83,14%</t>
+          <t>83,77%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,95%</t>
+          <t>80,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,84%</t>
+          <t>86,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>866867</t>
+          <t>904523</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>839536</t>
+          <t>879081</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>889477</t>
+          <t>928901</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>83,89%</t>
+          <t>83,97%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>81,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,08%</t>
+          <t>86,24%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>59697</t>
+          <t>60977</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>47955</t>
+          <t>48971</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>73736</t>
+          <t>73595</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>75065</t>
+          <t>75641</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>63134</t>
+          <t>65264</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>87360</t>
+          <t>87887</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>134763</t>
+          <t>136617</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>117871</t>
+          <t>118814</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>153029</t>
+          <t>153907</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>22,89%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>256353</t>
+          <t>255016</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>242314</t>
+          <t>242398</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>268095</t>
+          <t>267022</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>81,11%</t>
+          <t>80,7%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,67%</t>
+          <t>76,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>84,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>274063</t>
+          <t>280740</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>261768</t>
+          <t>268494</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>285994</t>
+          <t>291117</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>78,5%</t>
+          <t>78,78%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,98%</t>
+          <t>75,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>81,69%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>530415</t>
+          <t>535758</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>512149</t>
+          <t>518468</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>547307</t>
+          <t>553561</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>79,74%</t>
+          <t>79,68%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>76,99%</t>
+          <t>77,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>82,33%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>67475</t>
+          <t>84307</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>52674</t>
+          <t>65378</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>86615</t>
+          <t>108356</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>81489</t>
+          <t>89145</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>47671</t>
+          <t>75682</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>105493</t>
+          <t>102708</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>148964</t>
+          <t>173452</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>106087</t>
+          <t>150416</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>178899</t>
+          <t>201695</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>25,37%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>245082</t>
+          <t>288838</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>225942</t>
+          <t>264789</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>259883</t>
+          <t>307767</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>78,41%</t>
+          <t>77,41%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,29%</t>
+          <t>70,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,15%</t>
+          <t>82,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>394229</t>
+          <t>332816</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>370225</t>
+          <t>319253</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>428047</t>
+          <t>346279</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>78,87%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,82%</t>
+          <t>75,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>82,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>639310</t>
+          <t>621655</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>609375</t>
+          <t>593412</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>682187</t>
+          <t>644691</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>81,1%</t>
+          <t>78,19%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,31%</t>
+          <t>74,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,54%</t>
+          <t>81,08%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>44213</t>
+          <t>50987</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>34892</t>
+          <t>40270</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>54133</t>
+          <t>62285</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>41179</t>
+          <t>43880</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>23169</t>
+          <t>36418</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>55331</t>
+          <t>52871</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
+          <t>19,17%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
           <t>15,91%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>8,95%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>85392</t>
+          <t>94867</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>54335</t>
+          <t>82177</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>100247</t>
+          <t>108872</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>25,05%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>134529</t>
+          <t>154678</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>124609</t>
+          <t>143380</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>143850</t>
+          <t>165395</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>75,26%</t>
+          <t>75,21%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>69,71%</t>
+          <t>69,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>80,48%</t>
+          <t>80,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,34 +12217,34 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>217600</t>
+          <t>185038</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>203448</t>
+          <t>176047</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>235610</t>
+          <t>192500</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
+          <t>80,83%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>76,9%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
           <t>84,09%</t>
         </is>
       </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>78,62%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>91,05%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>595</t>
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>352129</t>
+          <t>339715</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>337274</t>
+          <t>325710</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>383186</t>
+          <t>352405</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>80,48%</t>
+          <t>78,17%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,09%</t>
+          <t>74,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>81,09%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>72481</t>
+          <t>73711</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>60067</t>
+          <t>61548</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>86218</t>
+          <t>86343</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>53474</t>
+          <t>56000</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>44339</t>
+          <t>47159</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>63406</t>
+          <t>66051</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>125955</t>
+          <t>129711</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>110087</t>
+          <t>114770</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>142269</t>
+          <t>146517</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>27,41%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>197155</t>
+          <t>196996</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>183418</t>
+          <t>184364</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>209569</t>
+          <t>209159</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>73,12%</t>
+          <t>72,77%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>68,02%</t>
+          <t>68,1%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>77,72%</t>
+          <t>77,26%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>203582</t>
+          <t>207750</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>193650</t>
+          <t>197699</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>212717</t>
+          <t>216591</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>79,2%</t>
+          <t>78,77%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>75,33%</t>
+          <t>74,96%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>82,75%</t>
+          <t>82,12%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>400737</t>
+          <t>404746</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>384423</t>
+          <t>387940</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>416605</t>
+          <t>419687</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>76,09%</t>
+          <t>75,73%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>72,99%</t>
+          <t>72,59%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>79,1%</t>
+          <t>78,53%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>109292</t>
+          <t>129645</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>90810</t>
+          <t>106051</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>129231</t>
+          <t>152639</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>87571</t>
+          <t>105248</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>42336</t>
+          <t>90285</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>120909</t>
+          <t>122016</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>196863</t>
+          <t>234893</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>125588</t>
+          <t>211419</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>240460</t>
+          <t>262669</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>17,61%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>514987</t>
+          <t>590042</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>495048</t>
+          <t>567048</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>533469</t>
+          <t>613636</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>82,49%</t>
+          <t>81,99%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>78,79%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>85,26%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>761694</t>
+          <t>666809</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>728356</t>
+          <t>650041</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>806929</t>
+          <t>681772</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>86,37%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>85,76%</t>
+          <t>84,2%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>88,31%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1276681</t>
+          <t>1256851</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1233084</t>
+          <t>1229075</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1347956</t>
+          <t>1280325</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>84,25%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>82,39%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>85,83%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>91598</t>
+          <t>109570</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>39422</t>
+          <t>89405</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>132333</t>
+          <t>128849</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>132983</t>
+          <t>152147</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>115610</t>
+          <t>134208</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>151426</t>
+          <t>174502</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>224581</t>
+          <t>261717</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>139440</t>
+          <t>230955</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>272983</t>
+          <t>289751</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>17,78%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>837122</t>
+          <t>688502</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>796387</t>
+          <t>669223</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>889298</t>
+          <t>708667</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>86,27%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
+          <t>83,85%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>584748</t>
+          <t>679184</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>566305</t>
+          <t>656829</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>602121</t>
+          <t>697123</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>81,47%</t>
+          <t>81,7%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>78,9%</t>
+          <t>79,01%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>83,89%</t>
+          <t>83,86%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1421871</t>
+          <t>1367686</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1373469</t>
+          <t>1339652</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1507012</t>
+          <t>1398448</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>83,94%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>83,42%</t>
+          <t>82,22%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>85,83%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>579391</t>
+          <t>650977</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>465285</t>
+          <t>601919</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>645945</t>
+          <t>699677</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>602510</t>
+          <t>657534</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>493102</t>
+          <t>618777</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>660438</t>
+          <t>694281</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1181902</t>
+          <t>1308510</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1029354</t>
+          <t>1249391</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1279637</t>
+          <t>1369989</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>18,85%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2880426</t>
+          <t>2881785</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2813872</t>
+          <t>2833085</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2994532</t>
+          <t>2930843</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>83,25%</t>
+          <t>81,57%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>81,33%</t>
+          <t>80,19%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>82,96%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3109770</t>
+          <t>3079420</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3051842</t>
+          <t>3042673</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3219178</t>
+          <t>3118177</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>83,77%</t>
+          <t>82,4%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>82,21%</t>
+          <t>81,42%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>86,72%</t>
+          <t>83,44%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>5990195</t>
+          <t>5961206</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5892460</t>
+          <t>5899727</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6142743</t>
+          <t>6020325</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>83,52%</t>
+          <t>82,0%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>82,16%</t>
+          <t>81,15%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>82,81%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">

--- a/data/trans_orig/P1_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P1_R-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares unipersonales en 2007 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si conforma un hogar unipersonal en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares unipersonales en 2012 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si conforma un hogar unipersonal en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares unipersonales en 2016 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si conforma un hogar unipersonal en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares unipersonales en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si conforma un hogar unipersonal en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
